--- a/services_forms/002_gym_cleaning_checklist--services_forms.xlsx
+++ b/services_forms/002_gym_cleaning_checklist--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -650,8 +650,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,12 +679,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'locker_rooms',_'text':_'locker_rooms'}</t>
+          <t>locker_rooms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Locker Rooms', 'text': 'Locker Rooms'}</t>
+          <t>Locker Rooms</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'showering_areas',_'text':_'showering_areas'}</t>
+          <t>showering_areas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Showering Areas', 'text': 'Showering Areas'}</t>
+          <t>Showering Areas</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'sauna',_'text':_'sauna'}</t>
+          <t>sauna</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Sauna', 'text': 'Sauna'}</t>
+          <t>Sauna</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'restrooms',_'text':_'restrooms'}</t>
+          <t>restrooms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Restrooms', 'text': 'Restrooms'}</t>
+          <t>Restrooms</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'exercise_rooms',_'text':_'exercise_rooms'}</t>
+          <t>exercise_rooms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Exercise Rooms', 'text': 'Exercise Rooms'}</t>
+          <t>Exercise Rooms</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'treadmill',_'text':_'treadmill'}</t>
+          <t>treadmill</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Treadmill', 'text': 'Treadmill'}</t>
+          <t>Treadmill</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'exercise_bike',_'text':_'exercise_bike'}</t>
+          <t>exercise_bike</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Exercise Bike', 'text': 'Exercise Bike'}</t>
+          <t>Exercise Bike</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'weights',_'text':_'weights'}</t>
+          <t>weights</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Weights', 'text': 'Weights'}</t>
+          <t>Weights</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'resistance_machines',_'text':_'resistance_machines'}</t>
+          <t>resistance_machines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Resistance Machines', 'text': 'Resistance Machines'}</t>
+          <t>Resistance Machines</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'daily',_'text':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Daily', 'text': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'weekly',_'text':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly', 'text': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'text':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly', 'text': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'quarterly',_'text':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterly', 'text': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'yearly',_'text':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Yearly', 'text': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'sanitation',_'text':_'sanitation'}</t>
+          <t>sanitation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Sanitation', 'text': 'Sanitation'}</t>
+          <t>Sanitation</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'hygiene',_'text':_'hygiene'}</t>
+          <t>hygiene</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Hygiene', 'text': 'Hygiene'}</t>
+          <t>Hygiene</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'organization',_'text':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Organization', 'text': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
